--- a/data/trans_orig/IP05B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05B-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>37676</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94323</t>
+          <t>94356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111540</t>
+          <t>111227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107934</t>
+          <t>106833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125869</t>
+          <t>123960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206115</t>
+          <t>207115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>230827</t>
+          <t>232387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>28869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48305</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45024</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28958</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46136</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>61862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>85494</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111494</t>
+          <t>113545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132665</t>
+          <t>134296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131324</t>
+          <t>131218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152669</t>
+          <t>152899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249737</t>
+          <t>251295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279246</t>
+          <t>281225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>32788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65043</t>
+          <t>66297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41472</t>
+          <t>41605</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47706</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>61907</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>84031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>80530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96892</t>
+          <t>96761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85434</t>
+          <t>84992</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103475</t>
+          <t>102929</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170867</t>
+          <t>171127</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195660</t>
+          <t>195563</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51286</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73905</t>
+          <t>75723</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78223</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>114280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>145204</t>
+          <t>146080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104740</t>
+          <t>103662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129382</t>
+          <t>128186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96307</t>
+          <t>97636</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121877</t>
+          <t>120502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208073</t>
+          <t>208195</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242147</t>
+          <t>241383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49675</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
+          <t>129566</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163121</t>
+          <t>164779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140224</t>
+          <t>139914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174449</t>
+          <t>175532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>279920</t>
+          <t>278649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>331962</t>
+          <t>329088</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>411640</t>
+          <t>410425</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>452777</t>
+          <t>452197</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>441836</t>
+          <t>443374</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>482870</t>
+          <t>482392</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>864439</t>
+          <t>867001</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>922481</t>
+          <t>921253</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>63982</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90374</t>
+          <t>90932</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66437</t>
+          <t>67079</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>93231</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136102</t>
+          <t>138522</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>175642</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96064</t>
+          <t>96442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113016</t>
+          <t>113201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102312</t>
+          <t>99835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120804</t>
+          <t>119286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205240</t>
+          <t>203482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227930</t>
+          <t>228730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44752</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70103</t>
+          <t>72262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34981</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32939</t>
+          <t>32985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40442</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62914</t>
+          <t>62007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145476</t>
+          <t>145859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165880</t>
+          <t>165253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166245</t>
+          <t>165687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186378</t>
+          <t>186886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317814</t>
+          <t>318897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345445</t>
+          <t>345616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26138</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>39037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59399</t>
+          <t>60387</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97060</t>
+          <t>97848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116367</t>
+          <t>116094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106842</t>
+          <t>105986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125464</t>
+          <t>125080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>209606</t>
+          <t>210368</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235848</t>
+          <t>236260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>56279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>824</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38649</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59377</t>
+          <t>58915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>51444</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>75604</t>
+          <t>76072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>103789</t>
+          <t>103716</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130832</t>
+          <t>132323</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>154156</t>
+          <t>154466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132112</t>
+          <t>130177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155063</t>
+          <t>153533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270657</t>
+          <t>270850</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303111</t>
+          <t>302022</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40581</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,42 +7158,42 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>11311</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2394</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>10572</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,47 +7266,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>20429</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>13970</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>29862</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>20429</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>13676</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>29674</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90886</t>
+          <t>91233</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>122458</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86061</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116284</t>
+          <t>117067</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>186518</t>
+          <t>184441</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230468</t>
+          <t>227281</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>493658</t>
+          <t>494033</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>531448</t>
+          <t>533298</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>527141</t>
+          <t>527775</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>566935</t>
+          <t>566293</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1029434</t>
+          <t>1032057</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1086650</t>
+          <t>1089373</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93435</t>
+          <t>91657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>76181</t>
+          <t>76216</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>105152</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>148268</t>
+          <t>147835</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>189728</t>
+          <t>189162</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>65071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83686</t>
+          <t>83759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70140</t>
+          <t>71282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>91930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143041</t>
+          <t>143034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171772</t>
+          <t>169484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42699</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61137</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96214</t>
+          <t>96454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122682</t>
+          <t>123781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23878</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>46583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>118611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135213</t>
+          <t>134049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158348</t>
+          <t>157735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261973</t>
+          <t>258893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>291612</t>
+          <t>291128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44946</t>
+          <t>45415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64574</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67990</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97984</t>
+          <t>97960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125837</t>
+          <t>127525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32162</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35714</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41578</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>62983</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76042</t>
+          <t>75803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95501</t>
+          <t>94289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86757</t>
+          <t>85872</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107233</t>
+          <t>107269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168879</t>
+          <t>166829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197210</t>
+          <t>196286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30981</t>
+          <t>30831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47235</t>
+          <t>47438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49346</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65682</t>
+          <t>66290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90693</t>
+          <t>91816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29630</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45635</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>61392</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89193</t>
+          <t>88526</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126304</t>
+          <t>125197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>148496</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129466</t>
+          <t>129820</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>150931</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262475</t>
+          <t>263133</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>295772</t>
+          <t>295240</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34696</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>41042</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62124</t>
+          <t>62234</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,47 +10795,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>6474</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>11355</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103261</t>
+          <t>104643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>101903</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>154914</t>
+          <t>155146</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196224</t>
+          <t>196394</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>407538</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>449317</t>
+          <t>448179</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>444786</t>
+          <t>444823</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>487632</t>
+          <t>486019</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>866538</t>
+          <t>862887</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>923895</t>
+          <t>925337</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153802</t>
+          <t>151254</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>189987</t>
+          <t>189226</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>160275</t>
+          <t>161254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>196552</t>
+          <t>198323</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>322510</t>
+          <t>321932</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>375675</t>
+          <t>374741</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75074</t>
+          <t>75249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83221</t>
+          <t>84806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108096</t>
+          <t>109052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147310</t>
+          <t>147011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178398</t>
+          <t>178512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37417</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54374</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55387</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73325</t>
+          <t>73326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103566</t>
+          <t>103074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124947</t>
+          <t>124630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146251</t>
+          <t>146272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182217</t>
+          <t>182908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207289</t>
+          <t>207523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>315976</t>
+          <t>316336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348392</t>
+          <t>347739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33098</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52724</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>37242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61298</t>
+          <t>60082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74713</t>
+          <t>75302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104499</t>
+          <t>104904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97720</t>
+          <t>99992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120449</t>
+          <t>129080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34833</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77512</t>
+          <t>74926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153884</t>
+          <t>155467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125781</t>
+          <t>126327</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152400</t>
+          <t>152708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198408</t>
+          <t>205016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>299014</t>
+          <t>297996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>44200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69308</t>
+          <t>70633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50578</t>
+          <t>49609</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118716</t>
+          <t>117939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136127</t>
+          <t>135309</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127753</t>
+          <t>129929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148370</t>
+          <t>148953</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>252317</t>
+          <t>255117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280354</t>
+          <t>281762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24399</t>
+          <t>24028</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38618</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>151151</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65769</t>
+          <t>63997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>77524</t>
+          <t>75235</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109196</t>
+          <t>108821</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>398278</t>
+          <t>401067</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>484861</t>
+          <t>486425</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>551129</t>
+          <t>551811</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>596911</t>
+          <t>598862</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>970085</t>
+          <t>963060</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1067562</t>
+          <t>1069687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>103757</t>
+          <t>103565</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>142706</t>
+          <t>141688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>115272</t>
+          <t>116583</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>158708</t>
+          <t>159472</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230447</t>
+          <t>231868</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>286843</t>
+          <t>290849</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
